--- a/assets/progress-template.xlsx
+++ b/assets/progress-template.xlsx
@@ -1,34 +1,17 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>SheetJS</Application>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>Worksheets</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>5</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="5" baseType="lpstr">
-      <vt:lpstr>填报说明</vt:lpstr>
-      <vt:lpstr>机电单位</vt:lpstr>
-      <vt:lpstr>消防单位</vt:lpstr>
-      <vt:lpstr>智能化单位</vt:lpstr>
-      <vt:lpstr>电梯单位</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <sheets>
+    <sheet name="填报说明" sheetId="1" r:id="rId1"/>
+    <sheet name="机电单位" sheetId="2" r:id="rId2"/>
+    <sheet name="消防单位" sheetId="3" r:id="rId3"/>
+    <sheet name="智能化单位" sheetId="4" r:id="rId4"/>
+  </sheets>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance"/>
-</file>
-
-<file path=xl\metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
@@ -50,7 +33,7 @@
 </metadata>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
@@ -95,7 +78,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -415,20 +398,7 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
-  <sheets>
-    <sheet name="填报说明" sheetId="1" r:id="rId1"/>
-    <sheet name="机电单位" sheetId="2" r:id="rId2"/>
-    <sheet name="消防单位" sheetId="3" r:id="rId3"/>
-    <sheet name="智能化单位" sheetId="4" r:id="rId4"/>
-    <sheet name="电梯单位" sheetId="5" r:id="rId5"/>
-  </sheets>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B9"/>
   <sheetData>
@@ -462,6 +432,11 @@
         <v>5. 完成率为 100% 时建议同步填写实际完成日期。</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6. 地下室部位进度统一按完成百分比填写，不使用实际完成情况。</v>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="str">
         <v>当前项目</v>
@@ -476,11 +451,6 @@
       </c>
       <c r="B9" t="str">
         <v>2026-05-08</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6. 地下室部位进度统一按完成百分比填写，不使用实际完成情况。</v>
       </c>
     </row>
   </sheetData>
@@ -491,7 +461,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F671"/>
   <sheetData>
@@ -13923,7 +13893,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F550"/>
   <sheetData>
@@ -24935,7 +24905,7 @@
 </worksheet>
 </file>
 
-<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F245"/>
   <sheetData>
@@ -29845,159 +29815,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:F245"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>楼栋</v>
-      </c>
-      <c r="B1" t="str">
-        <v>专业</v>
-      </c>
-      <c r="C1" t="str">
-        <v>电梯数量</v>
-      </c>
-      <c r="D1" t="str">
-        <v>已安装数量</v>
-      </c>
-      <c r="E1" t="str">
-        <v>完成百分比</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>A1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>电梯</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2">
-        <f>IFERROR(D2/C2*100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>A2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>电梯</v>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3">
-        <f>IFERROR(D3/C3*100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>B1</v>
-      </c>
-      <c r="B4" t="str">
-        <v>电梯</v>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4">
-        <f>IFERROR(D4/C4*100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>B2</v>
-      </c>
-      <c r="B5" t="str">
-        <v>电梯</v>
-      </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5">
-        <f>IFERROR(D5/C5*100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>B3</v>
-      </c>
-      <c r="B6" t="str">
-        <v>电梯</v>
-      </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6">
-        <f>IFERROR(D6/C6*100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>B4</v>
-      </c>
-      <c r="B7" t="str">
-        <v>电梯</v>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7">
-        <f>IFERROR(D7/C7*100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>B5</v>
-      </c>
-      <c r="B8" t="str">
-        <v>电梯</v>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8">
-        <f>IFERROR(D8/C8*100,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
-  </ignoredErrors>
-</worksheet>
 </file>